--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487436_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487436_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9143</v>
+        <v>8.7424</v>
       </c>
       <c r="E2" t="n">
-        <v>9.584899999999999</v>
+        <v>10.1724</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6706</v>
+        <v>-1.43</v>
       </c>
       <c r="G2" t="n">
         <v>8.7773</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9794</v>
+        <v>-0.1513</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2923</v>
+        <v>0.2952</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6871</v>
+        <v>-0.4465</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2754</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9712</v>
+        <v>3.0573</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2024</v>
+        <v>2.2618</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7688</v>
+        <v>0.7955</v>
       </c>
       <c r="G3" t="n">
         <v>0.7018</v>
@@ -688,13 +688,13 @@
         <v>0.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1543</v>
+        <v>0.2404</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2247</v>
+        <v>0.2841</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0704</v>
+        <v>-0.0437</v>
       </c>
       <c r="V3" t="n">
         <v>1.3318</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9186</v>
+        <v>2.9829</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4408</v>
+        <v>3.3714</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5222</v>
+        <v>-0.3885</v>
       </c>
       <c r="G4" t="n">
         <v>1.5839</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0362</v>
+        <v>0.0281</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4493</v>
+        <v>0.3799</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4855</v>
+        <v>-0.3518</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0312</v>
+        <v>1.6147</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0537</v>
+        <v>2.3004</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0224</v>
+        <v>-0.6856</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0434</v>
+        <v>0.6524</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8354</v>
+        <v>-1.7622</v>
       </c>
       <c r="I5" t="n">
-        <v>2.208</v>
+        <v>2.4145</v>
       </c>
       <c r="J5" t="n">
-        <v>4.756</v>
+        <v>1.794</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6948</v>
+        <v>0.4814</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0612</v>
+        <v>1.3126</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2874</v>
+        <v>-1.1416</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1406</v>
+        <v>-2.2436</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1468</v>
+        <v>1.102</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2252</v>
+        <v>0.2585</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6099</v>
+        <v>0.5064</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3847</v>
+        <v>-0.2479</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.0415</v>
+        <v>-0.2754</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7086</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7724</v>
+        <v>1.5733</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9769</v>
+        <v>3.5155</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2045</v>
+        <v>-1.9422</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6524</v>
+        <v>5.0434</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7622</v>
+        <v>2.8354</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4145</v>
+        <v>2.208</v>
       </c>
       <c r="J6" t="n">
-        <v>1.794</v>
+        <v>4.756</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4814</v>
+        <v>2.6948</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3126</v>
+        <v>2.0612</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1416</v>
+        <v>0.2874</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2436</v>
+        <v>0.1406</v>
       </c>
       <c r="O6" t="n">
-        <v>1.102</v>
+        <v>0.1468</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4162</v>
+        <v>-0.2328</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1829</v>
+        <v>0.0717</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2333</v>
+        <v>-0.3045</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>-3.0415</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4298</v>
+        <v>-0.0307</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4554</v>
+        <v>2.8812</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8852</v>
+        <v>-2.9119</v>
       </c>
       <c r="G7" t="n">
         <v>1.8547</v>
@@ -1000,13 +1000,13 @@
         <v>0.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1094</v>
+        <v>-0.7103</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9504</v>
+        <v>-0.5246</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.159</v>
+        <v>-0.1857</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.8699</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5824</v>
+        <v>-0.5065</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1763</v>
+        <v>-0.3634</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4867</v>
@@ -1078,13 +1078,13 @@
         <v>1.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2547</v>
+        <v>-0.366</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.31</v>
+        <v>-0.2341</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0552</v>
+        <v>-0.1319</v>
       </c>
       <c r="V8" t="n">
         <v>2.7662</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0188</v>
+        <v>-0.8792</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6021</v>
+        <v>-1.5427</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5833</v>
+        <v>0.6635</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0905</v>
@@ -1156,13 +1156,13 @@
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.457</v>
+        <v>-0.3174</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2376</v>
+        <v>-0.1782</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2194</v>
+        <v>-0.1392</v>
       </c>
       <c r="V9" t="n">
         <v>0.3329</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1914</v>
+        <v>-1.96</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0572</v>
+        <v>-0.8525</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1075</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1112</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.101</v>
+        <v>0.1304</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1188</v>
+        <v>0.0859</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8443</v>
+        <v>-2.678</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.357</v>
+        <v>-2.2976</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4873</v>
+        <v>-0.3804</v>
       </c>
       <c r="G11" t="n">
         <v>-2.165</v>
@@ -1312,13 +1312,13 @@
         <v>0.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1836</v>
+        <v>0.3499</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3381</v>
+        <v>-0.2311</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2754</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.3648</v>
+        <v>11.5528</v>
       </c>
       <c r="E12" t="n">
-        <v>18.11539999999999</v>
+        <v>19.3034</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.7506</v>
+        <v>-7.750500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>11.7601</v>
@@ -1390,22 +1390,22 @@
         <v>7.8338</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9584</v>
+        <v>-0.7704999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0793999999999998</v>
+        <v>1.2674</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0379</v>
+        <v>-2.0377</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5632</v>
+        <v>0.5631999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>5.0843</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.5212</v>
+        <v>-4.521199999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6646</v>
+        <v>3.2034</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2273</v>
+        <v>3.8969</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5627</v>
+        <v>-0.6935</v>
       </c>
       <c r="G13" t="n">
         <v>0.0607</v>
@@ -1468,13 +1468,13 @@
         <v>0.9792</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8366</v>
+        <v>1.3754</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1108</v>
+        <v>0.7804</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7258</v>
+        <v>0.5949</v>
       </c>
       <c r="V13" t="n">
         <v>1.7673</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6276</v>
+        <v>2.7106</v>
       </c>
       <c r="E14" t="n">
         <v>2.7181</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0905</v>
+        <v>-0.0075</v>
       </c>
       <c r="G14" t="n">
         <v>1.3657</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0061</v>
+        <v>0.0891</v>
       </c>
       <c r="T14" t="n">
         <v>0.1235</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1174</v>
+        <v>-0.0344</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1152</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6495</v>
+        <v>2.0573</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9552</v>
+        <v>4.8763</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3057</v>
+        <v>-2.819</v>
       </c>
       <c r="G15" t="n">
         <v>3.0883</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2107</v>
+        <v>0.197</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8975</v>
+        <v>0.0235</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3132</v>
+        <v>0.1735</v>
       </c>
       <c r="V15" t="n">
         <v>1.7097</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1714</v>
+        <v>-0.8598</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1028</v>
+        <v>0.3075</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2742</v>
+        <v>-1.1673</v>
       </c>
       <c r="G16" t="n">
         <v>0.4605</v>
@@ -1702,13 +1702,13 @@
         <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.2464</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2794</v>
+        <v>-0.0747</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2142</v>
+        <v>0.3211</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BARRIO</t>
+          <t>M. PEREIRA NIETO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7912</v>
+        <v>-1.9955</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6998</v>
+        <v>0.6912</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0914</v>
+        <v>-2.6867</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1205</v>
+        <v>-1.7854</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3879</v>
+        <v>2.0596</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7327</v>
+        <v>-3.845</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.581</v>
+        <v>0.4136</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0204</v>
+        <v>2.5315</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6014</v>
+        <v>-2.1179</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5396</v>
+        <v>-2.1989</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4083</v>
+        <v>-0.4718</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1313</v>
+        <v>-1.7271</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3917</v>
+        <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2374</v>
+        <v>0.3026</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1188</v>
+        <v>0.4734</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1186</v>
+        <v>-0.1708</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8249</v>
+        <v>-1.492</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8249</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PEREIRA NIETO</t>
+          <t>J. RODRIGUEZ BARRIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.945</v>
+        <v>-2.7645</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2818</v>
+        <v>-0.6998</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2269</v>
+        <v>-2.0647</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7854</v>
+        <v>-1.1205</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0596</v>
+        <v>-0.3879</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.845</v>
+        <v>-0.7327</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4136</v>
+        <v>-0.581</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5315</v>
+        <v>0.0204</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.1179</v>
+        <v>-0.6014</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1989</v>
+        <v>-0.5396</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4718</v>
+        <v>-0.4083</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7271</v>
+        <v>-0.1313</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6469</v>
+        <v>-0.2107</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0641</v>
+        <v>-0.1188</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7111</v>
+        <v>-0.0919</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.492</v>
+        <v>-1.8249</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.492</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.6105</v>
+        <v>-5.5026</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2001</v>
+        <v>-1.3278</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.4104</v>
+        <v>-4.1748</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.9959</v>
+        <v>-5.8334</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.191</v>
+        <v>-3.0956</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.8049</v>
+        <v>-2.7378</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.3106</v>
+        <v>-1.6597</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6317</v>
+        <v>-1.0582</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6789</v>
+        <v>-0.6014</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.6853</v>
+        <v>-4.1738</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5593</v>
+        <v>-2.0373</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1261</v>
+        <v>-2.1364</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0145</v>
+        <v>0.5474</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0898</v>
+        <v>0.2523</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.2951</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.7885</v>
+        <v>-5.8492</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6348</v>
+        <v>-2.7117</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.1537</v>
+        <v>-3.1375</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.8334</v>
+        <v>-7.9959</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.0956</v>
+        <v>-3.191</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7378</v>
+        <v>-4.8049</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6597</v>
+        <v>-4.3106</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0582</v>
+        <v>-1.6317</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6014</v>
+        <v>-2.6789</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.1738</v>
+        <v>-3.6853</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0373</v>
+        <v>-1.5593</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1364</v>
+        <v>-2.1261</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2615</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0547</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3162</v>
+        <v>0.1976</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8837</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.3649</v>
+        <v>-9.000300000000003</v>
       </c>
       <c r="E21" t="n">
-        <v>7.750499999999999</v>
+        <v>7.7507</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.1155</v>
+        <v>-16.751</v>
       </c>
       <c r="G21" t="n">
         <v>-11.76</v>
@@ -2092,13 +2092,13 @@
         <v>7.8339</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9585</v>
+        <v>3.3229</v>
       </c>
       <c r="T21" t="n">
-        <v>2.0378</v>
+        <v>2.0377</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.07939999999999992</v>
+        <v>1.2851</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5633999999999997</v>
